--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>day</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>final price</t>
+  </si>
+  <si>
+    <t>MIXED REFRENCE</t>
   </si>
 </sst>
 </file>
@@ -67,12 +70,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -87,9 +96,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -394,7 +410,7 @@
     <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -411,7 +427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -430,7 +446,7 @@
         <v>29500</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -446,8 +462,21 @@
         <f t="shared" ref="E3:E8" si="1">B3+D3</f>
         <v>33040</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -463,8 +492,38 @@
         <f t="shared" si="1"/>
         <v>36580</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="N4">
+        <v>7</v>
+      </c>
+      <c r="O4">
+        <v>8</v>
+      </c>
+      <c r="P4">
+        <v>9</v>
+      </c>
+      <c r="Q4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -480,8 +539,19 @@
         <f t="shared" si="1"/>
         <v>40120</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4">
+        <f>$G5*H$4</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <f>$H5*I$4</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -497,8 +567,19 @@
         <f t="shared" si="1"/>
         <v>43660</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="G6" s="4">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4">
+        <f>$G6*H$4</f>
+        <v>2</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" ref="I6:I14" si="2">$H6*I$4</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -514,8 +595,19 @@
         <f t="shared" si="1"/>
         <v>47200</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="G7" s="4">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4">
+        <f>$G7*H$4</f>
+        <v>3</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -531,8 +623,100 @@
         <f t="shared" si="1"/>
         <v>50740</v>
       </c>
+      <c r="G8" s="4">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4">
+        <f>$G8*H$4</f>
+        <v>4</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="G9" s="4">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4">
+        <f>$G9*H$4</f>
+        <v>5</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="G10" s="4">
+        <v>6</v>
+      </c>
+      <c r="H10" s="4">
+        <f>$G10*H$4</f>
+        <v>6</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="G11" s="4">
+        <v>7</v>
+      </c>
+      <c r="H11" s="4">
+        <f>$G11*H$4</f>
+        <v>7</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="G12" s="4">
+        <v>8</v>
+      </c>
+      <c r="H12" s="4">
+        <f>$G12*H$4</f>
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="G13" s="4">
+        <v>9</v>
+      </c>
+      <c r="H13" s="4">
+        <f>$G13*H$4</f>
+        <v>9</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="G14" s="4">
+        <v>10</v>
+      </c>
+      <c r="H14" s="4">
+        <f>$G14*H$4</f>
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G3:Q3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
